--- a/jogos_2025-01-14.xlsx
+++ b/jogos_2025-01-14.xlsx
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,19 +772,19 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Lamphun Warrior</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nakhon Ratchasima</t>
+          <t>Nam Dinh</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -798,83 +798,83 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.63</v>
+        <v>2.75</v>
       </c>
       <c r="M3" t="n">
-        <v>3.83</v>
+        <v>3.2</v>
       </c>
       <c r="N3" t="n">
-        <v>4.72</v>
+        <v>2.3</v>
       </c>
       <c r="O3" t="n">
-        <v>2.12</v>
+        <v>3.25</v>
       </c>
       <c r="P3" t="n">
-        <v>2.23</v>
+        <v>2.1</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.05</v>
+        <v>3</v>
       </c>
       <c r="R3" t="n">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="S3" t="n">
-        <v>3.04</v>
+        <v>2.75</v>
       </c>
       <c r="T3" t="n">
-        <v>2.59</v>
+        <v>2.8</v>
       </c>
       <c r="U3" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X3" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>['88']</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>['70']</t>
+        </is>
+      </c>
+      <c r="AG3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AH3" t="n">
         <v>1.44</v>
       </c>
-      <c r="V3" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X3" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>['47', '54', '90+3']</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG3" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>2.14</v>
-      </c>
       <c r="AI3" t="n">
-        <v>1.45</v>
+        <v>2.2</v>
       </c>
       <c r="AJ3" t="n">
-        <v>2.84</v>
+        <v>1.8</v>
       </c>
       <c r="AK3" s="3" t="n">
         <v>45671.33333333334</v>
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,19 +901,19 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>Lamphun Warrior</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nam Dinh</t>
+          <t>Nakhon Ratchasima</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -927,83 +927,83 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.75</v>
+        <v>1.63</v>
       </c>
       <c r="M4" t="n">
-        <v>3.2</v>
+        <v>3.83</v>
       </c>
       <c r="N4" t="n">
-        <v>2.3</v>
+        <v>4.72</v>
       </c>
       <c r="O4" t="n">
-        <v>3.25</v>
+        <v>2.12</v>
       </c>
       <c r="P4" t="n">
-        <v>2.1</v>
+        <v>2.23</v>
       </c>
       <c r="Q4" t="n">
-        <v>3</v>
+        <v>5.05</v>
       </c>
       <c r="R4" t="n">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="S4" t="n">
-        <v>2.75</v>
+        <v>3.04</v>
       </c>
       <c r="T4" t="n">
-        <v>2.8</v>
+        <v>2.59</v>
       </c>
       <c r="U4" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="V4" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="W4" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="X4" t="n">
-        <v>3.35</v>
+        <v>3.68</v>
       </c>
       <c r="Y4" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Z4" t="n">
         <v>1.95</v>
       </c>
-      <c r="Z4" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AA4" t="n">
-        <v>3.1</v>
+        <v>2.83</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.65</v>
+        <v>1.76</v>
       </c>
       <c r="AD4" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>['88']</t>
+          <t>['47', '54', '90+3']</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>['70']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.5</v>
+        <v>1.11</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.44</v>
+        <v>2.14</v>
       </c>
       <c r="AI4" t="n">
-        <v>2.2</v>
+        <v>1.45</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.8</v>
+        <v>2.84</v>
       </c>
       <c r="AK4" s="3" t="n">
         <v>45671.33333333334</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,22 +1546,22 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1572,83 +1572,83 @@
         </is>
       </c>
       <c r="L9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="N9" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>6</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X9" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB9" t="n">
         <v>1.6</v>
       </c>
-      <c r="M9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="N9" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="O9" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="P9" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S9" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X9" t="n">
-        <v>6</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="AA9" t="n">
+      <c r="AC9" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD9" t="n">
         <v>2</v>
       </c>
-      <c r="AB9" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>2.5</v>
-      </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>['13', '90+5']</t>
+          <t>['48']</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>['50', '68']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.25</v>
+        <v>2.65</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AJ9" t="n">
-        <v>2.75</v>
+        <v>3.4</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45671.6875</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,22 +1675,22 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1701,83 +1701,83 @@
         </is>
       </c>
       <c r="L10" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="M10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="O10" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S10" t="n">
+        <v>4</v>
+      </c>
+      <c r="T10" t="n">
         <v>2</v>
       </c>
-      <c r="M10" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="N10" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="O10" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="P10" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.25</v>
-      </c>
       <c r="U10" t="n">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="V10" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W10" t="n">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="X10" t="n">
-        <v>5</v>
+        <v>6.8</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.35</v>
+        <v>2.9</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.38</v>
+        <v>2.63</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>['3', '60', '75', '84', '87']</t>
+          <t>['82', '90+2']</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>['89']</t>
+          <t>['66', '78']</t>
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.29</v>
+        <v>2.2</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.57</v>
+        <v>2.63</v>
       </c>
       <c r="AJ10" t="n">
-        <v>2.38</v>
+        <v>1.44</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45671.6875</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,22 +1804,22 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1830,83 +1830,83 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>4.8</v>
+        <v>2</v>
       </c>
       <c r="M11" t="n">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="N11" t="n">
-        <v>1.6</v>
+        <v>3.6</v>
       </c>
       <c r="O11" t="n">
-        <v>4.33</v>
+        <v>2.5</v>
       </c>
       <c r="P11" t="n">
-        <v>2.63</v>
+        <v>2.4</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.1</v>
+        <v>3.75</v>
       </c>
       <c r="R11" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="S11" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="T11" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="U11" t="n">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="V11" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W11" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="X11" t="n">
-        <v>6.8</v>
+        <v>5</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.9</v>
+        <v>2.35</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.63</v>
+        <v>2.38</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>['82', '90+2']</t>
+          <t>['3', '60', '75', '84', '87']</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>['66', '78']</t>
+          <t>['89']</t>
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>2.2</v>
+        <v>1.29</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="AI11" t="n">
-        <v>2.63</v>
+        <v>1.57</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.44</v>
+        <v>2.38</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45671.6875</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,22 +1933,22 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1959,83 +1959,83 @@
         </is>
       </c>
       <c r="L12" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="M12" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="N12" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="O12" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X12" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>['13', '90+5']</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>['50', '68']</t>
+        </is>
+      </c>
+      <c r="AG12" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AI12" t="n">
         <v>1.4</v>
       </c>
-      <c r="M12" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="N12" t="n">
-        <v>7.25</v>
-      </c>
-      <c r="O12" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="P12" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>6</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S12" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X12" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE12" t="inlineStr">
-        <is>
-          <t>['48']</t>
-        </is>
-      </c>
-      <c r="AF12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AJ12" t="n">
-        <v>3.4</v>
+        <v>2.75</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45671.6875</v>
@@ -2449,22 +2449,22 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Barry Town United</t>
+          <t>Newtown</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Haverfordwest County</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="G16" t="n">
         <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
         <v>1</v>
@@ -2475,83 +2475,83 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.3</v>
+        <v>4.75</v>
       </c>
       <c r="M16" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="N16" t="n">
-        <v>1.83</v>
+        <v>1.53</v>
       </c>
       <c r="O16" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="P16" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="R16" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="S16" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="T16" t="n">
-        <v>2.63</v>
+        <v>2.38</v>
       </c>
       <c r="U16" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="V16" t="n">
         <v>1.01</v>
       </c>
       <c r="W16" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="X16" t="n">
-        <v>3.68</v>
+        <v>4.05</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.59</v>
+        <v>2.35</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.39</v>
+        <v>1.47</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.1</v>
+        <v>1.73</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>['24']</t>
+          <t>['51']</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>['1']</t>
+          <t>['5', '47']</t>
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.73</v>
+        <v>2.65</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.27</v>
+        <v>1.1</v>
       </c>
       <c r="AI16" t="n">
-        <v>2.4</v>
+        <v>4</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.57</v>
+        <v>1.25</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45671.69791666666</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,19 +2578,19 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Caernarfon Town</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Flint Town United</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -2604,83 +2604,83 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="M17" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="N17" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="O17" t="n">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="P17" t="n">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.25</v>
+        <v>4.33</v>
       </c>
       <c r="R17" t="n">
-        <v>1.29</v>
+        <v>1.44</v>
       </c>
       <c r="S17" t="n">
-        <v>3.5</v>
+        <v>2.63</v>
       </c>
       <c r="T17" t="n">
-        <v>2.25</v>
+        <v>3</v>
       </c>
       <c r="U17" t="n">
-        <v>1.57</v>
+        <v>1.36</v>
       </c>
       <c r="V17" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="W17" t="n">
-        <v>1.12</v>
+        <v>1.33</v>
       </c>
       <c r="X17" t="n">
-        <v>4.75</v>
+        <v>3.3</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.45</v>
+        <v>1.95</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.55</v>
+        <v>1.77</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.2</v>
+        <v>3.6</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.58</v>
+        <v>1.3</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.44</v>
+        <v>1.8</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.63</v>
+        <v>1.95</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>['47', '80', '84']</t>
+          <t>['78']</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['54']</t>
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.58</v>
+        <v>1.75</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AJ17" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45671.69791666666</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Cardiff MU</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2725,7 +2725,7 @@
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -2733,62 +2733,62 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.85</v>
+        <v>6.5</v>
       </c>
       <c r="M18" t="n">
-        <v>2.9</v>
+        <v>4.5</v>
       </c>
       <c r="N18" t="n">
-        <v>2.3</v>
+        <v>1.33</v>
       </c>
       <c r="O18" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S18" t="n">
         <v>3.75</v>
       </c>
-      <c r="P18" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>3</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2.38</v>
-      </c>
       <c r="T18" t="n">
-        <v>3.5</v>
+        <v>2.1</v>
       </c>
       <c r="U18" t="n">
-        <v>1.29</v>
+        <v>1.67</v>
       </c>
       <c r="V18" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W18" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X18" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="Y18" t="n">
         <v>1.44</v>
       </c>
-      <c r="X18" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="Y18" t="n">
+      <c r="Z18" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD18" t="n">
         <v>2.2</v>
       </c>
-      <c r="Z18" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.67</v>
-      </c>
       <c r="AE18" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2796,20 +2796,20 @@
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>['61', '71']</t>
+          <t>['39', '89']</t>
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.6</v>
+        <v>2.5</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.36</v>
+        <v>1.1</v>
       </c>
       <c r="AI18" t="n">
-        <v>2.38</v>
+        <v>3.4</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45671.69791666666</v>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,19 +2836,19 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Caernarfon Town</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Flint Town United</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
@@ -2862,83 +2862,83 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="M19" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="N19" t="n">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="O19" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="P19" t="n">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.33</v>
+        <v>3.25</v>
       </c>
       <c r="R19" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X19" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AC19" t="n">
         <v>1.44</v>
       </c>
-      <c r="S19" t="n">
+      <c r="AD19" t="n">
         <v>2.63</v>
       </c>
-      <c r="T19" t="n">
-        <v>3</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="X19" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>['78']</t>
+          <t>['47', '80', '84']</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>['54']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.75</v>
+        <v>1.58</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AJ19" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45671.69791666666</v>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,16 +2965,16 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Newtown</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
         <v>2</v>
@@ -2983,7 +2983,7 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -2991,83 +2991,83 @@
         </is>
       </c>
       <c r="L20" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="M20" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N20" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="O20" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>3</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X20" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AA20" t="n">
         <v>4.75</v>
       </c>
-      <c r="M20" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="N20" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="O20" t="n">
-        <v>7</v>
-      </c>
-      <c r="P20" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q20" t="n">
+      <c r="AB20" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>['61', '71']</t>
+        </is>
+      </c>
+      <c r="AG20" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AJ20" t="n">
         <v>1.8</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S20" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="X20" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AE20" t="inlineStr">
-        <is>
-          <t>['51']</t>
-        </is>
-      </c>
-      <c r="AF20" t="inlineStr">
-        <is>
-          <t>['5', '47']</t>
-        </is>
-      </c>
-      <c r="AG20" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>4</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>1.25</v>
       </c>
       <c r="AK20" s="3" t="n">
         <v>45671.69791666666</v>
@@ -3094,22 +3094,22 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Cardiff MU</t>
+          <t>Barry Town United</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Haverfordwest County</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J21" t="n">
         <v>1</v>
@@ -3120,83 +3120,83 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>6.5</v>
+        <v>3.3</v>
       </c>
       <c r="M21" t="n">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="N21" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="O21" t="n">
+        <v>4</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R21" t="n">
         <v>1.33</v>
       </c>
-      <c r="O21" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="P21" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.25</v>
-      </c>
       <c r="S21" t="n">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="T21" t="n">
-        <v>2.1</v>
+        <v>2.63</v>
       </c>
       <c r="U21" t="n">
-        <v>1.67</v>
+        <v>1.44</v>
       </c>
       <c r="V21" t="n">
         <v>1.01</v>
       </c>
       <c r="W21" t="n">
-        <v>1.09</v>
+        <v>1.2</v>
       </c>
       <c r="X21" t="n">
-        <v>5.4</v>
+        <v>3.68</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.44</v>
+        <v>1.8</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.63</v>
+        <v>1.88</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.07</v>
+        <v>2.59</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.68</v>
+        <v>1.39</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['24']</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>['39', '89']</t>
+          <t>['1']</t>
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>2.5</v>
+        <v>1.73</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AI21" t="n">
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.3</v>
+        <v>1.57</v>
       </c>
       <c r="AK21" s="3" t="n">
         <v>45671.69791666666</v>
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3241,7 +3241,7 @@
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -3249,83 +3249,83 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="M22" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="N22" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="O22" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="P22" t="n">
         <v>2.2</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="R22" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="S22" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="T22" t="n">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="U22" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="V22" t="n">
         <v>1.05</v>
       </c>
       <c r="W22" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="X22" t="n">
-        <v>3.8</v>
+        <v>3.45</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.71</v>
+        <v>1.82</v>
       </c>
       <c r="Z22" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AA22" t="n">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AD22" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>['65']</t>
+          <t>['63']</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>['87']</t>
+          <t>['44']</t>
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="AI22" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AJ22" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AK22" s="3" t="n">
         <v>45671.69791666666</v>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3370,7 +3370,7 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -3378,83 +3378,83 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="M23" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="N23" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="O23" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="P23" t="n">
         <v>2.2</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="R23" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="S23" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="T23" t="n">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="U23" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="V23" t="n">
         <v>1.05</v>
       </c>
       <c r="W23" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="X23" t="n">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.82</v>
+        <v>1.71</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="AA23" t="n">
-        <v>3.35</v>
+        <v>3</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AD23" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>['63']</t>
+          <t>['65']</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>['44']</t>
+          <t>['87']</t>
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="AI23" t="n">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AJ23" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AK23" s="3" t="n">
         <v>45671.69791666666</v>
